--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.43101117043258</v>
+        <v>4.620039315195294</v>
       </c>
       <c r="D2" t="n">
-        <v>29.40001579774099</v>
+        <v>4.777502567132911</v>
       </c>
       <c r="E2" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F2" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.32949658601152</v>
+        <v>2.003543195226872</v>
       </c>
       <c r="D3" t="n">
-        <v>13.28414168903401</v>
+        <v>2.158673024468026</v>
       </c>
       <c r="E3" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F3" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.31578085952756</v>
+        <v>4.276314389673229</v>
       </c>
       <c r="D4" t="n">
-        <v>26.20278271905909</v>
+        <v>4.257952191847102</v>
       </c>
       <c r="E4" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F4" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.04853600684989</v>
+        <v>3.582887101113108</v>
       </c>
       <c r="D5" t="n">
-        <v>21.17134104775092</v>
+        <v>3.440342920259525</v>
       </c>
       <c r="E5" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F5" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.85945917683764</v>
+        <v>5.664662116236117</v>
       </c>
       <c r="D6" t="n">
-        <v>34.00540900187198</v>
+        <v>5.525878962804197</v>
       </c>
       <c r="E6" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F6" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.96399259948328</v>
+        <v>6.169148797416033</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00451920854236</v>
+        <v>6.013234371388133</v>
       </c>
       <c r="E7" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F7" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.73308309937054</v>
+        <v>2.881626003647712</v>
       </c>
       <c r="D8" t="n">
-        <v>18.94915738230596</v>
+        <v>3.079238074624718</v>
       </c>
       <c r="E8" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F8" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.83203034587103</v>
+        <v>4.685204931204042</v>
       </c>
       <c r="D9" t="n">
-        <v>27.24458461596039</v>
+        <v>4.427245000093563</v>
       </c>
       <c r="E9" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F9" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.96334184974101</v>
+        <v>5.519043050582915</v>
       </c>
       <c r="D10" t="n">
-        <v>33.80416293595931</v>
+        <v>5.493176477093388</v>
       </c>
       <c r="E10" t="n">
-        <v>7.901663943027069</v>
+        <v>1.284020390741899</v>
       </c>
       <c r="F10" t="n">
-        <v>7.366717958265951</v>
+        <v>1.197091668218217</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
